--- a/artfynd/A 18789-2025 artfynd.xlsx
+++ b/artfynd/A 18789-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111952091</v>
+        <v>111952094</v>
       </c>
       <c r="B2" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528949</v>
+        <v>529190</v>
       </c>
       <c r="R2" t="n">
-        <v>7048303</v>
+        <v>7048108</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111952088</v>
+        <v>111952096</v>
       </c>
       <c r="B3" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529102</v>
+        <v>529163</v>
       </c>
       <c r="R3" t="n">
-        <v>7048306</v>
+        <v>7048125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111952086</v>
+        <v>111952092</v>
       </c>
       <c r="B4" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529112</v>
+        <v>529100</v>
       </c>
       <c r="R4" t="n">
-        <v>7048267</v>
+        <v>7048311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111952089</v>
+        <v>111952093</v>
       </c>
       <c r="B5" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529022</v>
+        <v>528927</v>
       </c>
       <c r="R5" t="n">
-        <v>7048280</v>
+        <v>7048245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,12 +1082,7 @@
         <v>111952095</v>
       </c>
       <c r="B6" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111952096</v>
+        <v>111952086</v>
       </c>
       <c r="B7" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529163</v>
+        <v>529112</v>
       </c>
       <c r="R7" t="n">
-        <v>7048125</v>
+        <v>7048267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111952092</v>
+        <v>111952087</v>
       </c>
       <c r="B8" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529099</v>
+        <v>529142</v>
       </c>
       <c r="R8" t="n">
-        <v>7048311</v>
+        <v>7048300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111952094</v>
+        <v>111952088</v>
       </c>
       <c r="B9" t="n">
-        <v>89549</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529190</v>
+        <v>529101</v>
       </c>
       <c r="R9" t="n">
-        <v>7048108</v>
+        <v>7048306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111952087</v>
+        <v>111952089</v>
       </c>
       <c r="B10" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529142</v>
+        <v>529022</v>
       </c>
       <c r="R10" t="n">
-        <v>7048300</v>
+        <v>7048280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111952084</v>
+        <v>111952091</v>
       </c>
       <c r="B11" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529035</v>
+        <v>528950</v>
       </c>
       <c r="R11" t="n">
-        <v>7048206</v>
+        <v>7048303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,112 +1678,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>111952093</v>
-      </c>
-      <c r="B12" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Stortjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>528926</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7048245</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 18789-2025 artfynd.xlsx
+++ b/artfynd/A 18789-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952094</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952092</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952086</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952087</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952088</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,8 +1732,25 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>